--- a/output/pdf_financials_xlsx/EXG.xlsx
+++ b/output/pdf_financials_xlsx/EXG.xlsx
@@ -1385,19 +1385,19 @@
         <v>-0.550105</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.673185</v>
+        <v>-0.673185</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.355557</v>
+        <v>-0.355557</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>11.843216</v>
+        <v>-11.843216</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.669163</v>
+        <v>-1.599163</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.157279</v>
+        <v>-0.157279</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-0.290042</v>
@@ -1709,19 +1709,19 @@
         <v>-0.550105</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.673185</v>
+        <v>-0.673185</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.355557</v>
+        <v>-0.355557</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>11.843216</v>
+        <v>-11.843216</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.634163</v>
+        <v>-1.634163</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.157279</v>
+        <v>-0.157279</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-0.290042</v>
@@ -1904,19 +1904,19 @@
         <v>-0.550105</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.673185</v>
+        <v>-0.673185</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.355557</v>
+        <v>-0.355557</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>11.843216</v>
+        <v>-11.843216</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.634163</v>
+        <v>-1.634163</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.157279</v>
+        <v>-0.157279</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-0.290042</v>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>296.0804</v>
+        <v>-296.0804</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -2200,19 +2200,19 @@
         <v>-0.550105</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.673185</v>
+        <v>-0.673185</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.355557</v>
+        <v>-0.355557</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>11.843216</v>
+        <v>-11.843216</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.669163</v>
+        <v>-1.599163</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.157279</v>
+        <v>-0.157279</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.290042</v>
@@ -2330,19 +2330,19 @@
         <v>-0.548326</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.674608</v>
+        <v>-0.671762</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.355842</v>
+        <v>-0.355272</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>11.843216</v>
+        <v>-11.843216</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.669163</v>
+        <v>-1.599163</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.157279</v>
+        <v>-0.157279</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.290042</v>
@@ -2492,19 +2492,19 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>2.096859324104356</v>
+        <v>-2.18864493488156</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -6419,34 +6419,34 @@
         <v>3.498504</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>3.977292</v>
+        <v>4.181714</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>3.977292</v>
+        <v>4.286714</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>3.977292</v>
+        <v>4.472714</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4.184944</v>
+        <v>4.472714</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>4.184944</v>
+        <v>4.472714</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>4.286644</v>
+        <v>4.472714</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>4.286644</v>
+        <v>4.915324</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>4.286644</v>
+        <v>4.915324</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>4.286644</v>
+        <v>4.915324</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>4.286644</v>
+        <v>5.124701</v>
       </c>
     </row>
     <row r="93">
@@ -11024,7 +11024,11 @@
           <t>Reserves (note 15)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -12246,7 +12250,11 @@
           <t>Reserves (note 8)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -13492,7 +13500,11 @@
           <t>Warrants reserve (note 8)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -14536,7 +14548,11 @@
           <t>Warrants reserve (note 9)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -15816,7 +15832,11 @@
           <t>Warrants reserve (note 8(c))</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -51438,10 +51458,10 @@
         </is>
       </c>
       <c r="O402" s="5" t="n">
-        <v>0.157279</v>
+        <v>-0.157279</v>
       </c>
       <c r="P402" s="5" t="n">
-        <v>0.290042</v>
+        <v>-0.290042</v>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -51750,10 +51770,10 @@
         </is>
       </c>
       <c r="O405" s="5" t="n">
-        <v>0.546778</v>
+        <v>-0.546778</v>
       </c>
       <c r="P405" s="5" t="n">
-        <v>0.5496490000000001</v>
+        <v>-0.5496490000000001</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
@@ -53520,13 +53540,13 @@
         </is>
       </c>
       <c r="M422" s="5" t="n">
-        <v>11.843216</v>
+        <v>-11.843216</v>
       </c>
       <c r="N422" s="5" t="n">
-        <v>1.634163</v>
+        <v>-1.634163</v>
       </c>
       <c r="O422" s="5" t="n">
-        <v>0.157279</v>
+        <v>-0.157279</v>
       </c>
       <c r="P422" t="inlineStr">
         <is>
@@ -55307,10 +55327,10 @@
         </is>
       </c>
       <c r="L439" s="5" t="n">
-        <v>0.355557</v>
+        <v>-0.355557</v>
       </c>
       <c r="M439" s="5" t="n">
-        <v>11.843216</v>
+        <v>-11.843216</v>
       </c>
       <c r="N439" t="inlineStr">
         <is>
@@ -56366,10 +56386,10 @@
         </is>
       </c>
       <c r="K449" s="5" t="n">
-        <v>0.673185</v>
+        <v>-0.673185</v>
       </c>
       <c r="L449" s="5" t="n">
-        <v>0.355557</v>
+        <v>-0.355557</v>
       </c>
       <c r="M449" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EXG.xlsx
+++ b/output/pdf_financials_xlsx/EXG.xlsx
@@ -1152,13 +1152,13 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.053167</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.075296</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.116823</v>
       </c>
     </row>
     <row r="13">
@@ -2227,13 +2227,13 @@
         <v>-0.568398</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.185526</v>
+        <v>-0.238693</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.246056</v>
+        <v>-0.321352</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.9597020000000001</v>
+        <v>-1.076525</v>
       </c>
     </row>
     <row r="28">
@@ -2357,13 +2357,13 @@
         <v>-0.568398</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.185526</v>
+        <v>-0.238693</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.246056</v>
+        <v>-0.321352</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.9597020000000001</v>
+        <v>-1.076525</v>
       </c>
     </row>
     <row r="30">
@@ -2654,31 +2654,31 @@
         <v>1.981356</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.435469</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.432559</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.150492</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.089577</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.31307</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.269988</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.277399</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.232725</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.486822</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>2.628135</v>
@@ -2687,10 +2687,10 @@
         <v>3.264429</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>3.64072</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>2.24527</v>
       </c>
     </row>
     <row r="35">
@@ -2776,31 +2776,31 @@
         <v>1.981356</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.435469</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.432559</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.150492</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.654577</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.822092</v>
+        <v>1.135162</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.560993</v>
+        <v>0.830981</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.296713</v>
+        <v>0.574112</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.91311</v>
+        <v>1.145835</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.224</v>
+        <v>1.710822</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>3.27982</v>
@@ -2809,10 +2809,10 @@
         <v>3.780285</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.132887</v>
+        <v>3.773607</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.074753</v>
+        <v>2.320023</v>
       </c>
     </row>
     <row r="37">
@@ -3508,13 +3508,13 @@
         <v>0.022343</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.453669</v>
+        <v>0.0182</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.440259</v>
+        <v>0.0077</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.158192</v>
+        <v>0.0077</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -3532,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.486822</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0</v>
@@ -3541,10 +3541,10 @@
         <v>0.963768</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>3.939922</v>
+        <v>0.299202</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>2.666094</v>
+        <v>0.420824</v>
       </c>
     </row>
     <row r="49">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -40054,7 +40054,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -44438,7 +44438,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -54862,7 +54862,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -56032,7 +56032,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -56994,7 +56994,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
